--- a/test_phase_200.xlsx
+++ b/test_phase_200.xlsx
@@ -738,113 +738,113 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>-76</v>
+        <v>-331</v>
       </c>
       <c r="B2">
-        <v>-121</v>
+        <v>-189</v>
       </c>
       <c r="C2">
-        <v>-174</v>
+        <v>-119</v>
       </c>
       <c r="D2">
-        <v>-125</v>
+        <v>-183</v>
       </c>
       <c r="E2">
-        <v>-221</v>
+        <v>-32</v>
       </c>
       <c r="F2">
-        <v>-25</v>
+        <v>-256</v>
       </c>
       <c r="G2">
-        <v>22</v>
+        <v>339</v>
       </c>
       <c r="H2">
-        <v>175</v>
+        <v>34</v>
       </c>
       <c r="I2">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="J2">
+        <v>114</v>
+      </c>
+      <c r="K2">
+        <v>193</v>
+      </c>
+      <c r="L2">
+        <v>43</v>
+      </c>
+      <c r="M2">
+        <v>-115</v>
+      </c>
+      <c r="N2">
+        <v>-343</v>
+      </c>
+      <c r="O2">
+        <v>-183</v>
+      </c>
+      <c r="P2">
+        <v>342</v>
+      </c>
+      <c r="Q2">
+        <v>43</v>
+      </c>
+      <c r="R2">
+        <v>268</v>
+      </c>
+      <c r="S2">
+        <v>-106</v>
+      </c>
+      <c r="T2">
+        <v>-337</v>
+      </c>
+      <c r="U2">
+        <v>-269</v>
+      </c>
+      <c r="V2">
+        <v>189</v>
+      </c>
+      <c r="W2">
+        <v>108</v>
+      </c>
+      <c r="X2">
+        <v>265</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
         <v>180</v>
-      </c>
-      <c r="K2">
-        <v>125</v>
-      </c>
-      <c r="L2">
-        <v>221</v>
-      </c>
-      <c r="M2">
-        <v>-29</v>
-      </c>
-      <c r="N2">
-        <v>-71</v>
-      </c>
-      <c r="O2">
-        <v>-124</v>
-      </c>
-      <c r="P2">
-        <v>129</v>
-      </c>
-      <c r="Q2">
-        <v>73</v>
-      </c>
-      <c r="R2">
-        <v>230</v>
-      </c>
-      <c r="S2">
-        <v>-24</v>
-      </c>
-      <c r="T2">
-        <v>-223</v>
-      </c>
-      <c r="U2">
-        <v>-79</v>
-      </c>
-      <c r="V2">
-        <v>75</v>
-      </c>
-      <c r="W2">
-        <v>229</v>
-      </c>
-      <c r="X2">
-        <v>21</v>
-      </c>
-      <c r="Y2">
-        <v>270</v>
-      </c>
-      <c r="Z2">
-        <v>180</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
       </c>
       <c r="AB2">
         <v>180</v>
       </c>
       <c r="AC2">
+        <v>90</v>
+      </c>
+      <c r="AD2">
+        <v>270</v>
+      </c>
+      <c r="AE2">
+        <v>90</v>
+      </c>
+      <c r="AF2">
+        <v>180</v>
+      </c>
+      <c r="AG2">
+        <v>90</v>
+      </c>
+      <c r="AH2">
         <v>0</v>
       </c>
-      <c r="AD2">
-        <v>90</v>
-      </c>
-      <c r="AE2">
+      <c r="AI2">
         <v>270</v>
       </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
+      <c r="AJ2">
         <v>270</v>
       </c>
-      <c r="AH2">
-        <v>180</v>
-      </c>
-      <c r="AI2">
-        <v>90</v>
-      </c>
-      <c r="AJ2">
-        <v>90</v>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -877,7 +877,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -902,11 +902,11 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AW2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -919,82 +919,82 @@
         </is>
       </c>
       <c r="AZ2">
-        <v>-225</v>
+        <v>-187.5</v>
       </c>
       <c r="BA2">
-        <v>225</v>
+        <v>337.5</v>
       </c>
       <c r="BB2">
-        <v>-125</v>
+        <v>-337.5</v>
       </c>
       <c r="BC2">
-        <v>-225</v>
+        <v>-112.5</v>
       </c>
       <c r="BD2">
-        <v>-25</v>
+        <v>337.5</v>
       </c>
       <c r="BE2">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="BF2">
-        <v>125</v>
+        <v>112.5</v>
       </c>
       <c r="BG2">
-        <v>-75</v>
+        <v>-337.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>black</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>violet</t>
-        </is>
-      </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>d</t>
         </is>
       </c>
       <c r="BN2">
-        <v>-225</v>
+        <v>187.5</v>
       </c>
       <c r="BO2">
-        <v>225</v>
+        <v>-262.5</v>
       </c>
       <c r="BP2">
-        <v>-125</v>
+        <v>-337.5</v>
       </c>
       <c r="BQ2">
-        <v>-225</v>
+        <v>-112.5</v>
       </c>
       <c r="BR2">
-        <v>-25</v>
+        <v>337.5</v>
       </c>
       <c r="BS2">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="BT2">
-        <v>125</v>
+        <v>112.5</v>
       </c>
       <c r="BU2">
-        <v>-75</v>
+        <v>-337.5</v>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
@@ -1014,103 +1014,103 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>-79</v>
+        <v>-33</v>
       </c>
       <c r="B3">
-        <v>-180</v>
+        <v>-189</v>
       </c>
       <c r="C3">
-        <v>-128</v>
+        <v>-112</v>
       </c>
       <c r="D3">
-        <v>-123</v>
+        <v>-116</v>
       </c>
       <c r="E3">
-        <v>-173</v>
+        <v>-39</v>
       </c>
       <c r="F3">
-        <v>-75</v>
+        <v>-194</v>
       </c>
       <c r="G3">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="H3">
-        <v>75</v>
+        <v>263</v>
       </c>
       <c r="I3">
-        <v>222</v>
+        <v>39</v>
       </c>
       <c r="J3">
-        <v>122</v>
+        <v>342</v>
       </c>
       <c r="K3">
-        <v>227</v>
+        <v>40</v>
       </c>
       <c r="L3">
-        <v>30</v>
+        <v>269</v>
       </c>
       <c r="M3">
-        <v>-79</v>
+        <v>-192</v>
       </c>
       <c r="N3">
-        <v>-21</v>
+        <v>-107</v>
       </c>
       <c r="O3">
-        <v>-172</v>
+        <v>-34</v>
       </c>
       <c r="P3">
-        <v>126</v>
+        <v>257</v>
       </c>
       <c r="Q3">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="R3">
-        <v>70</v>
+        <v>342</v>
       </c>
       <c r="S3">
-        <v>-72</v>
+        <v>-109</v>
       </c>
       <c r="T3">
-        <v>-222</v>
+        <v>-30</v>
       </c>
       <c r="U3">
-        <v>-176</v>
+        <v>-338</v>
       </c>
       <c r="V3">
-        <v>72</v>
+        <v>261</v>
       </c>
       <c r="W3">
-        <v>122</v>
+        <v>344</v>
       </c>
       <c r="X3">
-        <v>224</v>
+        <v>107</v>
       </c>
       <c r="Y3">
         <v>180</v>
       </c>
       <c r="Z3">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AA3">
         <v>270</v>
       </c>
       <c r="AB3">
+        <v>90</v>
+      </c>
+      <c r="AC3">
         <v>0</v>
       </c>
-      <c r="AC3">
-        <v>90</v>
-      </c>
       <c r="AD3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>180</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AG3">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AH3">
         <v>270</v>
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
@@ -1195,44 +1195,44 @@
         </is>
       </c>
       <c r="AZ3">
-        <v>125</v>
+        <v>-187.5</v>
       </c>
       <c r="BA3">
-        <v>-75</v>
+        <v>187.5</v>
       </c>
       <c r="BB3">
-        <v>-225</v>
+        <v>37.5</v>
       </c>
       <c r="BC3">
-        <v>125</v>
+        <v>337.5</v>
       </c>
       <c r="BD3">
-        <v>-125</v>
+        <v>-337.5</v>
       </c>
       <c r="BE3">
-        <v>25</v>
+        <v>-112.5</v>
       </c>
       <c r="BF3">
-        <v>-25</v>
+        <v>187.5</v>
       </c>
       <c r="BG3">
-        <v>-225</v>
+        <v>37.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>white</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>violet</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>yellow</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
       <c r="BK3" t="inlineStr">
         <is>
           <t>green</t>
@@ -1249,28 +1249,28 @@
         </is>
       </c>
       <c r="BN3">
-        <v>125</v>
+        <v>-187.5</v>
       </c>
       <c r="BO3">
-        <v>-75</v>
+        <v>187.5</v>
       </c>
       <c r="BP3">
-        <v>-225</v>
+        <v>37.5</v>
       </c>
       <c r="BQ3">
-        <v>125</v>
+        <v>337.5</v>
       </c>
       <c r="BR3">
-        <v>-125</v>
+        <v>-337.5</v>
       </c>
       <c r="BS3">
-        <v>25</v>
+        <v>-112.5</v>
       </c>
       <c r="BT3">
-        <v>-25</v>
+        <v>187.5</v>
       </c>
       <c r="BU3">
-        <v>-225</v>
+        <v>37.5</v>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
@@ -1290,85 +1290,85 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>-76</v>
+        <v>-338</v>
       </c>
       <c r="B4">
-        <v>-22</v>
+        <v>-270</v>
       </c>
       <c r="C4">
-        <v>-174</v>
+        <v>-107</v>
       </c>
       <c r="D4">
-        <v>-71</v>
+        <v>-259</v>
       </c>
       <c r="E4">
-        <v>-171</v>
+        <v>-36</v>
       </c>
       <c r="F4">
-        <v>-130</v>
+        <v>-110</v>
       </c>
       <c r="G4">
-        <v>224</v>
+        <v>108</v>
       </c>
       <c r="H4">
-        <v>124</v>
+        <v>257</v>
       </c>
       <c r="I4">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="J4">
-        <v>227</v>
+        <v>331</v>
       </c>
       <c r="K4">
-        <v>128</v>
+        <v>35</v>
       </c>
       <c r="L4">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="M4">
-        <v>-73</v>
+        <v>-262</v>
       </c>
       <c r="N4">
-        <v>-126</v>
+        <v>-117</v>
       </c>
       <c r="O4">
-        <v>-173</v>
+        <v>-34</v>
       </c>
       <c r="P4">
-        <v>29</v>
+        <v>265</v>
       </c>
       <c r="Q4">
-        <v>123</v>
+        <v>337</v>
       </c>
       <c r="R4">
-        <v>170</v>
+        <v>43</v>
       </c>
       <c r="S4">
-        <v>-225</v>
+        <v>-116</v>
       </c>
       <c r="T4">
-        <v>-29</v>
+        <v>-40</v>
       </c>
       <c r="U4">
-        <v>-121</v>
+        <v>-268</v>
       </c>
       <c r="V4">
-        <v>71</v>
+        <v>263</v>
       </c>
       <c r="W4">
-        <v>172</v>
+        <v>342</v>
       </c>
       <c r="X4">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="Y4">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="Z4">
         <v>270</v>
       </c>
       <c r="AA4">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AB4">
         <v>90</v>
@@ -1377,25 +1377,25 @@
         <v>180</v>
       </c>
       <c r="AD4">
+        <v>90</v>
+      </c>
+      <c r="AE4">
         <v>180</v>
       </c>
-      <c r="AE4">
+      <c r="AF4">
         <v>270</v>
       </c>
-      <c r="AF4">
-        <v>90</v>
-      </c>
       <c r="AG4">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AH4">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AI4">
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1471,28 +1471,28 @@
         </is>
       </c>
       <c r="AZ4">
-        <v>-125</v>
+        <v>-187.5</v>
       </c>
       <c r="BA4">
-        <v>125</v>
+        <v>-112.5</v>
       </c>
       <c r="BB4">
-        <v>-225</v>
+        <v>-337.5</v>
       </c>
       <c r="BC4">
-        <v>-125</v>
+        <v>-262.5</v>
       </c>
       <c r="BD4">
-        <v>225</v>
+        <v>-37.5</v>
       </c>
       <c r="BE4">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="BF4">
-        <v>75</v>
+        <v>187.5</v>
       </c>
       <c r="BG4">
-        <v>225</v>
+        <v>337.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
@@ -1501,52 +1501,52 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
           <t>violet</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>yellow</t>
-        </is>
-      </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>s</t>
         </is>
       </c>
       <c r="BN4">
-        <v>225</v>
+        <v>-187.5</v>
       </c>
       <c r="BO4">
-        <v>-225</v>
+        <v>-112.5</v>
       </c>
       <c r="BP4">
-        <v>-225</v>
+        <v>-337.5</v>
       </c>
       <c r="BQ4">
-        <v>-125</v>
+        <v>-262.5</v>
       </c>
       <c r="BR4">
-        <v>225</v>
+        <v>-37.5</v>
       </c>
       <c r="BS4">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="BT4">
-        <v>75</v>
+        <v>187.5</v>
       </c>
       <c r="BU4">
-        <v>225</v>
+        <v>337.5</v>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
@@ -1566,112 +1566,112 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>-228</v>
+        <v>-343</v>
       </c>
       <c r="B5">
-        <v>-76</v>
+        <v>-185</v>
       </c>
       <c r="C5">
-        <v>-30</v>
+        <v>-42</v>
       </c>
       <c r="D5">
-        <v>-223</v>
+        <v>-191</v>
       </c>
       <c r="E5">
-        <v>-176</v>
+        <v>-42</v>
       </c>
       <c r="F5">
-        <v>-129</v>
+        <v>-269</v>
       </c>
       <c r="G5">
-        <v>23</v>
+        <v>193</v>
       </c>
       <c r="H5">
-        <v>129</v>
+        <v>35</v>
       </c>
       <c r="I5">
-        <v>72</v>
+        <v>259</v>
       </c>
       <c r="J5">
-        <v>229</v>
+        <v>340</v>
       </c>
       <c r="K5">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="L5">
-        <v>22</v>
+        <v>267</v>
       </c>
       <c r="M5">
-        <v>-229</v>
+        <v>-186</v>
       </c>
       <c r="N5">
-        <v>-129</v>
+        <v>-259</v>
       </c>
       <c r="O5">
-        <v>-77</v>
+        <v>-116</v>
       </c>
       <c r="P5">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="Q5">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="R5">
-        <v>222</v>
+        <v>331</v>
       </c>
       <c r="S5">
-        <v>-72</v>
+        <v>-340</v>
       </c>
       <c r="T5">
-        <v>-129</v>
+        <v>-120</v>
       </c>
       <c r="U5">
-        <v>-224</v>
+        <v>-41</v>
       </c>
       <c r="V5">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="W5">
-        <v>173</v>
+        <v>333</v>
       </c>
       <c r="X5">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="Y5">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="Z5">
         <v>270</v>
       </c>
       <c r="AA5">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AB5">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AC5">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AD5">
         <v>180</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AF5">
         <v>0</v>
       </c>
       <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>180</v>
+      </c>
+      <c r="AI5">
         <v>90</v>
       </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>270</v>
-      </c>
       <c r="AJ5">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -1730,15 +1730,15 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AW5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1747,44 +1747,44 @@
         </is>
       </c>
       <c r="AZ5">
-        <v>-75</v>
+        <v>262.5</v>
       </c>
       <c r="BA5">
-        <v>-175</v>
+        <v>262.5</v>
       </c>
       <c r="BB5">
-        <v>125</v>
+        <v>112.5</v>
       </c>
       <c r="BC5">
-        <v>-75</v>
+        <v>-37.5</v>
       </c>
       <c r="BD5">
-        <v>225</v>
+        <v>-187.5</v>
       </c>
       <c r="BE5">
-        <v>25</v>
+        <v>-337.5</v>
       </c>
       <c r="BF5">
-        <v>-225</v>
+        <v>-37.5</v>
       </c>
       <c r="BG5">
-        <v>175</v>
+        <v>112.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>violet</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
           <t>white</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>violet</t>
-        </is>
-      </c>
       <c r="BK5" t="inlineStr">
         <is>
           <t>green</t>
@@ -1801,28 +1801,28 @@
         </is>
       </c>
       <c r="BN5">
-        <v>-75</v>
+        <v>262.5</v>
       </c>
       <c r="BO5">
-        <v>-175</v>
+        <v>262.5</v>
       </c>
       <c r="BP5">
-        <v>125</v>
+        <v>112.5</v>
       </c>
       <c r="BQ5">
-        <v>-75</v>
+        <v>-37.5</v>
       </c>
       <c r="BR5">
-        <v>225</v>
+        <v>-187.5</v>
       </c>
       <c r="BS5">
-        <v>25</v>
+        <v>-337.5</v>
       </c>
       <c r="BT5">
-        <v>-225</v>
+        <v>-37.5</v>
       </c>
       <c r="BU5">
-        <v>175</v>
+        <v>112.5</v>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
@@ -1842,112 +1842,112 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>-128</v>
+        <v>-332</v>
       </c>
       <c r="B6">
-        <v>-221</v>
+        <v>-111</v>
       </c>
       <c r="C6">
-        <v>-178</v>
+        <v>-181</v>
       </c>
       <c r="D6">
-        <v>-225</v>
+        <v>-263</v>
       </c>
       <c r="E6">
-        <v>-127</v>
+        <v>-115</v>
       </c>
       <c r="F6">
-        <v>-27</v>
+        <v>-40</v>
       </c>
       <c r="G6">
-        <v>122</v>
+        <v>335</v>
       </c>
       <c r="H6">
-        <v>177</v>
+        <v>267</v>
       </c>
       <c r="I6">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J6">
-        <v>176</v>
+        <v>42</v>
       </c>
       <c r="K6">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="L6">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="M6">
-        <v>-229</v>
+        <v>-341</v>
       </c>
       <c r="N6">
-        <v>-77</v>
+        <v>-111</v>
       </c>
       <c r="O6">
-        <v>-176</v>
+        <v>-36</v>
       </c>
       <c r="P6">
-        <v>76</v>
+        <v>269</v>
       </c>
       <c r="Q6">
-        <v>27</v>
+        <v>336</v>
       </c>
       <c r="R6">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="S6">
-        <v>-174</v>
+        <v>-343</v>
       </c>
       <c r="T6">
-        <v>-125</v>
+        <v>-270</v>
       </c>
       <c r="U6">
-        <v>-21</v>
+        <v>-111</v>
       </c>
       <c r="V6">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="W6">
-        <v>121</v>
+        <v>333</v>
       </c>
       <c r="X6">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>180</v>
+      </c>
+      <c r="AA6">
         <v>270</v>
       </c>
-      <c r="Z6">
+      <c r="AB6">
+        <v>90</v>
+      </c>
+      <c r="AC6">
+        <v>270</v>
+      </c>
+      <c r="AD6">
         <v>0</v>
       </c>
-      <c r="AA6">
+      <c r="AE6">
+        <v>270</v>
+      </c>
+      <c r="AF6">
         <v>0</v>
       </c>
-      <c r="AB6">
+      <c r="AG6">
         <v>180</v>
       </c>
-      <c r="AC6">
+      <c r="AH6">
         <v>180</v>
-      </c>
-      <c r="AD6">
-        <v>90</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>180</v>
-      </c>
-      <c r="AG6">
-        <v>90</v>
-      </c>
-      <c r="AH6">
-        <v>270</v>
       </c>
       <c r="AI6">
         <v>90</v>
       </c>
       <c r="AJ6">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2006,11 +2006,11 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AW6">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -2023,47 +2023,47 @@
         </is>
       </c>
       <c r="AZ6">
-        <v>25</v>
+        <v>-337.5</v>
       </c>
       <c r="BA6">
-        <v>125</v>
+        <v>-37.5</v>
       </c>
       <c r="BB6">
-        <v>-175</v>
+        <v>37.5</v>
       </c>
       <c r="BC6">
-        <v>-225</v>
+        <v>-187.5</v>
       </c>
       <c r="BD6">
-        <v>-75</v>
+        <v>262.5</v>
       </c>
       <c r="BE6">
-        <v>-25</v>
+        <v>-337.5</v>
       </c>
       <c r="BF6">
-        <v>225</v>
+        <v>-187.5</v>
       </c>
       <c r="BG6">
-        <v>-125</v>
+        <v>187.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>red</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>violet</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>violet</t>
+          <t>black</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
@@ -2077,28 +2077,28 @@
         </is>
       </c>
       <c r="BN6">
-        <v>25</v>
+        <v>-337.5</v>
       </c>
       <c r="BO6">
-        <v>125</v>
+        <v>-37.5</v>
       </c>
       <c r="BP6">
-        <v>-175</v>
+        <v>37.5</v>
       </c>
       <c r="BQ6">
-        <v>-225</v>
+        <v>-187.5</v>
       </c>
       <c r="BR6">
-        <v>-75</v>
+        <v>262.5</v>
       </c>
       <c r="BS6">
-        <v>-25</v>
+        <v>-337.5</v>
       </c>
       <c r="BT6">
-        <v>225</v>
+        <v>-187.5</v>
       </c>
       <c r="BU6">
-        <v>-125</v>
+        <v>187.5</v>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
@@ -2118,103 +2118,103 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>-26</v>
+        <v>-114</v>
       </c>
       <c r="B7">
-        <v>-179</v>
+        <v>-343</v>
       </c>
       <c r="C7">
-        <v>-72</v>
+        <v>-186</v>
       </c>
       <c r="D7">
-        <v>-20</v>
+        <v>-35</v>
       </c>
       <c r="E7">
-        <v>-125</v>
+        <v>-119</v>
       </c>
       <c r="F7">
-        <v>-222</v>
+        <v>-189</v>
       </c>
       <c r="G7">
-        <v>24</v>
+        <v>191</v>
       </c>
       <c r="H7">
-        <v>77</v>
+        <v>265</v>
       </c>
       <c r="I7">
-        <v>125</v>
+        <v>334</v>
       </c>
       <c r="J7">
-        <v>129</v>
+        <v>38</v>
       </c>
       <c r="K7">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="L7">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="M7">
-        <v>-24</v>
+        <v>-341</v>
       </c>
       <c r="N7">
-        <v>-129</v>
+        <v>-182</v>
       </c>
       <c r="O7">
-        <v>-78</v>
+        <v>-258</v>
       </c>
       <c r="P7">
-        <v>172</v>
+        <v>259</v>
       </c>
       <c r="Q7">
-        <v>28</v>
+        <v>341</v>
       </c>
       <c r="R7">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="S7">
-        <v>-180</v>
+        <v>-344</v>
       </c>
       <c r="T7">
-        <v>-78</v>
+        <v>-113</v>
       </c>
       <c r="U7">
-        <v>-27</v>
+        <v>-32</v>
       </c>
       <c r="V7">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="W7">
-        <v>121</v>
+        <v>340</v>
       </c>
       <c r="X7">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="Y7">
         <v>90</v>
       </c>
       <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
         <v>180</v>
       </c>
-      <c r="AA7">
-        <v>90</v>
-      </c>
       <c r="AB7">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AC7">
         <v>270</v>
       </c>
       <c r="AD7">
+        <v>90</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
         <v>270</v>
       </c>
-      <c r="AE7">
-        <v>270</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
       <c r="AG7">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -2223,11 +2223,11 @@
         <v>180</v>
       </c>
       <c r="AJ7">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2286,11 +2286,11 @@
         </is>
       </c>
       <c r="AW7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -2299,47 +2299,47 @@
         </is>
       </c>
       <c r="AZ7">
-        <v>75</v>
+        <v>-262.5</v>
       </c>
       <c r="BA7">
-        <v>75</v>
+        <v>112.5</v>
       </c>
       <c r="BB7">
-        <v>225</v>
+        <v>-112.5</v>
       </c>
       <c r="BC7">
-        <v>-175</v>
+        <v>337.5</v>
       </c>
       <c r="BD7">
-        <v>-125</v>
+        <v>37.5</v>
       </c>
       <c r="BE7">
-        <v>225</v>
+        <v>-337.5</v>
       </c>
       <c r="BF7">
-        <v>-25</v>
+        <v>187.5</v>
       </c>
       <c r="BG7">
-        <v>-25</v>
+        <v>-187.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>yellow</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>green</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>red</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>black</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
@@ -2353,28 +2353,28 @@
         </is>
       </c>
       <c r="BN7">
-        <v>-125</v>
+        <v>262.5</v>
       </c>
       <c r="BO7">
-        <v>-75</v>
+        <v>-37.5</v>
       </c>
       <c r="BP7">
-        <v>225</v>
+        <v>-112.5</v>
       </c>
       <c r="BQ7">
-        <v>-175</v>
+        <v>337.5</v>
       </c>
       <c r="BR7">
-        <v>-125</v>
+        <v>37.5</v>
       </c>
       <c r="BS7">
-        <v>225</v>
+        <v>-337.5</v>
       </c>
       <c r="BT7">
-        <v>-25</v>
+        <v>187.5</v>
       </c>
       <c r="BU7">
-        <v>-25</v>
+        <v>-187.5</v>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
@@ -2394,112 +2394,112 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>-178</v>
+        <v>-185</v>
       </c>
       <c r="B8">
-        <v>-223</v>
+        <v>-333</v>
       </c>
       <c r="C8">
-        <v>-79</v>
+        <v>-269</v>
       </c>
       <c r="D8">
-        <v>-77</v>
+        <v>-183</v>
       </c>
       <c r="E8">
-        <v>-226</v>
+        <v>-340</v>
       </c>
       <c r="F8">
-        <v>-125</v>
+        <v>-34</v>
       </c>
       <c r="G8">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="H8">
-        <v>123</v>
+        <v>337</v>
       </c>
       <c r="I8">
-        <v>72</v>
+        <v>257</v>
       </c>
       <c r="J8">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="K8">
-        <v>24</v>
+        <v>270</v>
       </c>
       <c r="L8">
-        <v>130</v>
+        <v>337</v>
       </c>
       <c r="M8">
-        <v>-20</v>
+        <v>-39</v>
       </c>
       <c r="N8">
-        <v>-177</v>
+        <v>-267</v>
       </c>
       <c r="O8">
-        <v>-222</v>
+        <v>-106</v>
       </c>
       <c r="P8">
-        <v>20</v>
+        <v>338</v>
       </c>
       <c r="Q8">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="R8">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="S8">
-        <v>-225</v>
+        <v>-333</v>
       </c>
       <c r="T8">
-        <v>-70</v>
+        <v>-181</v>
       </c>
       <c r="U8">
-        <v>-120</v>
+        <v>-44</v>
       </c>
       <c r="V8">
-        <v>77</v>
+        <v>258</v>
       </c>
       <c r="W8">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="X8">
-        <v>172</v>
+        <v>40</v>
       </c>
       <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
         <v>90</v>
       </c>
-      <c r="Z8">
+      <c r="AC8">
+        <v>90</v>
+      </c>
+      <c r="AD8">
         <v>270</v>
       </c>
-      <c r="AA8">
+      <c r="AE8">
         <v>180</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>180</v>
-      </c>
-      <c r="AD8">
-        <v>180</v>
-      </c>
-      <c r="AE8">
-        <v>90</v>
       </c>
       <c r="AF8">
         <v>270</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AI8">
         <v>90</v>
       </c>
       <c r="AJ8">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2562,11 +2562,11 @@
         </is>
       </c>
       <c r="AW8">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -2575,47 +2575,47 @@
         </is>
       </c>
       <c r="AZ8">
-        <v>25</v>
+        <v>112.5</v>
       </c>
       <c r="BA8">
-        <v>225</v>
+        <v>112.5</v>
       </c>
       <c r="BB8">
-        <v>125</v>
+        <v>262.5</v>
       </c>
       <c r="BC8">
-        <v>25</v>
+        <v>-337.5</v>
       </c>
       <c r="BD8">
-        <v>-175</v>
+        <v>-37.5</v>
       </c>
       <c r="BE8">
-        <v>-75</v>
+        <v>-37.5</v>
       </c>
       <c r="BF8">
-        <v>-75</v>
+        <v>-337.5</v>
       </c>
       <c r="BG8">
-        <v>125</v>
+        <v>-187.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>violet</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>red</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>black</t>
-        </is>
-      </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>green</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>violet</t>
+          <t>white</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
@@ -2629,28 +2629,28 @@
         </is>
       </c>
       <c r="BN8">
-        <v>-175</v>
+        <v>-187.5</v>
       </c>
       <c r="BO8">
-        <v>-225</v>
+        <v>-37.5</v>
       </c>
       <c r="BP8">
-        <v>125</v>
+        <v>262.5</v>
       </c>
       <c r="BQ8">
-        <v>25</v>
+        <v>-337.5</v>
       </c>
       <c r="BR8">
-        <v>-175</v>
+        <v>-37.5</v>
       </c>
       <c r="BS8">
-        <v>-75</v>
+        <v>-37.5</v>
       </c>
       <c r="BT8">
-        <v>-75</v>
+        <v>-337.5</v>
       </c>
       <c r="BU8">
-        <v>125</v>
+        <v>-187.5</v>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
@@ -2670,112 +2670,112 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>-79</v>
+        <v>-186</v>
       </c>
       <c r="B9">
-        <v>-129</v>
+        <v>-256</v>
       </c>
       <c r="C9">
-        <v>-23</v>
+        <v>-105</v>
       </c>
       <c r="D9">
-        <v>-226</v>
+        <v>-30</v>
       </c>
       <c r="E9">
-        <v>-170</v>
+        <v>-332</v>
       </c>
       <c r="F9">
-        <v>-25</v>
+        <v>-256</v>
       </c>
       <c r="G9">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="H9">
-        <v>130</v>
+        <v>340</v>
       </c>
       <c r="I9">
-        <v>221</v>
+        <v>108</v>
       </c>
       <c r="J9">
-        <v>122</v>
+        <v>341</v>
       </c>
       <c r="K9">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="L9">
-        <v>173</v>
+        <v>257</v>
       </c>
       <c r="M9">
-        <v>-179</v>
+        <v>-339</v>
       </c>
       <c r="N9">
-        <v>-129</v>
+        <v>-181</v>
       </c>
       <c r="O9">
-        <v>-222</v>
+        <v>-109</v>
       </c>
       <c r="P9">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="Q9">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="R9">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="S9">
-        <v>-170</v>
+        <v>-109</v>
       </c>
       <c r="T9">
-        <v>-24</v>
+        <v>-194</v>
       </c>
       <c r="U9">
-        <v>-222</v>
+        <v>-32</v>
       </c>
       <c r="V9">
-        <v>224</v>
+        <v>341</v>
       </c>
       <c r="W9">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="X9">
-        <v>26</v>
+        <v>269</v>
       </c>
       <c r="Y9">
         <v>0</v>
       </c>
       <c r="Z9">
+        <v>270</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>270</v>
+      </c>
+      <c r="AC9">
         <v>180</v>
       </c>
-      <c r="AA9">
-        <v>270</v>
-      </c>
-      <c r="AB9">
+      <c r="AD9">
         <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>90</v>
-      </c>
-      <c r="AD9">
-        <v>90</v>
       </c>
       <c r="AE9">
         <v>270</v>
       </c>
       <c r="AF9">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AG9">
         <v>180</v>
       </c>
       <c r="AH9">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ9">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="AW9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2851,82 +2851,82 @@
         </is>
       </c>
       <c r="AZ9">
-        <v>-125</v>
+        <v>-112.5</v>
       </c>
       <c r="BA9">
-        <v>-25</v>
+        <v>-187.5</v>
       </c>
       <c r="BB9">
-        <v>-25</v>
+        <v>-337.5</v>
       </c>
       <c r="BC9">
-        <v>175</v>
+        <v>-337.5</v>
       </c>
       <c r="BD9">
-        <v>225</v>
+        <v>262.5</v>
       </c>
       <c r="BE9">
-        <v>75</v>
+        <v>112.5</v>
       </c>
       <c r="BF9">
-        <v>-225</v>
+        <v>112.5</v>
       </c>
       <c r="BG9">
-        <v>-125</v>
+        <v>-37.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>violet</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>yellow</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>white</t>
-        </is>
-      </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>d</t>
         </is>
       </c>
       <c r="BN9">
-        <v>-125</v>
+        <v>262.5</v>
       </c>
       <c r="BO9">
-        <v>-25</v>
+        <v>37.5</v>
       </c>
       <c r="BP9">
-        <v>-25</v>
+        <v>-337.5</v>
       </c>
       <c r="BQ9">
-        <v>175</v>
+        <v>-337.5</v>
       </c>
       <c r="BR9">
-        <v>225</v>
+        <v>262.5</v>
       </c>
       <c r="BS9">
-        <v>75</v>
+        <v>112.5</v>
       </c>
       <c r="BT9">
-        <v>-225</v>
+        <v>112.5</v>
       </c>
       <c r="BU9">
-        <v>-125</v>
+        <v>-37.5</v>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
@@ -2946,100 +2946,100 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>-128</v>
+        <v>-105</v>
       </c>
       <c r="B10">
-        <v>-71</v>
+        <v>-44</v>
       </c>
       <c r="C10">
-        <v>-176</v>
+        <v>-188</v>
       </c>
       <c r="D10">
-        <v>-127</v>
+        <v>-185</v>
       </c>
       <c r="E10">
-        <v>-20</v>
+        <v>-33</v>
       </c>
       <c r="F10">
-        <v>-74</v>
+        <v>-337</v>
       </c>
       <c r="G10">
-        <v>78</v>
+        <v>192</v>
       </c>
       <c r="H10">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="I10">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="J10">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="K10">
-        <v>171</v>
+        <v>256</v>
       </c>
       <c r="L10">
-        <v>122</v>
+        <v>338</v>
       </c>
       <c r="M10">
-        <v>-25</v>
+        <v>-30</v>
       </c>
       <c r="N10">
-        <v>-229</v>
+        <v>-114</v>
       </c>
       <c r="O10">
-        <v>-72</v>
+        <v>-269</v>
       </c>
       <c r="P10">
-        <v>122</v>
+        <v>331</v>
       </c>
       <c r="Q10">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="R10">
-        <v>222</v>
+        <v>44</v>
       </c>
       <c r="S10">
-        <v>-22</v>
+        <v>-180</v>
       </c>
       <c r="T10">
-        <v>-72</v>
+        <v>-32</v>
       </c>
       <c r="U10">
-        <v>-127</v>
+        <v>-111</v>
       </c>
       <c r="V10">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="W10">
-        <v>178</v>
+        <v>258</v>
       </c>
       <c r="X10">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="Y10">
+        <v>90</v>
+      </c>
+      <c r="Z10">
+        <v>90</v>
+      </c>
+      <c r="AA10">
+        <v>90</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
         <v>180</v>
       </c>
-      <c r="Z10">
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>180</v>
+      </c>
+      <c r="AF10">
         <v>270</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>90</v>
-      </c>
-      <c r="AC10">
-        <v>270</v>
-      </c>
-      <c r="AD10">
-        <v>90</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>180</v>
       </c>
       <c r="AG10">
         <v>180</v>
@@ -3048,7 +3048,7 @@
         <v>270</v>
       </c>
       <c r="AI10">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AJ10">
         <v>0</v>
@@ -3075,46 +3075,46 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>L0.png</t>
         </is>
       </c>
       <c r="AW10">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -3127,49 +3127,49 @@
         </is>
       </c>
       <c r="AZ10">
-        <v>-25</v>
+        <v>337.5</v>
       </c>
       <c r="BA10">
-        <v>-175</v>
+        <v>-262.5</v>
       </c>
       <c r="BB10">
-        <v>225</v>
+        <v>-187.5</v>
       </c>
       <c r="BC10">
-        <v>75</v>
+        <v>337.5</v>
       </c>
       <c r="BD10">
-        <v>-125</v>
+        <v>187.5</v>
       </c>
       <c r="BE10">
-        <v>-25</v>
+        <v>-112.5</v>
       </c>
       <c r="BF10">
-        <v>125</v>
+        <v>37.5</v>
       </c>
       <c r="BG10">
-        <v>175</v>
+        <v>187.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>violet</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>white</t>
-        </is>
-      </c>
       <c r="BL10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3181,28 +3181,28 @@
         </is>
       </c>
       <c r="BN10">
-        <v>-225</v>
+        <v>112.5</v>
       </c>
       <c r="BO10">
-        <v>175</v>
+        <v>37.5</v>
       </c>
       <c r="BP10">
-        <v>225</v>
+        <v>-187.5</v>
       </c>
       <c r="BQ10">
-        <v>75</v>
+        <v>337.5</v>
       </c>
       <c r="BR10">
-        <v>-125</v>
+        <v>187.5</v>
       </c>
       <c r="BS10">
-        <v>-25</v>
+        <v>-112.5</v>
       </c>
       <c r="BT10">
-        <v>125</v>
+        <v>37.5</v>
       </c>
       <c r="BU10">
-        <v>175</v>
+        <v>187.5</v>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
@@ -3222,113 +3222,113 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>-28</v>
+        <v>-115</v>
       </c>
       <c r="B11">
-        <v>-75</v>
+        <v>-343</v>
       </c>
       <c r="C11">
-        <v>-171</v>
+        <v>-262</v>
       </c>
       <c r="D11">
-        <v>-180</v>
+        <v>-257</v>
       </c>
       <c r="E11">
-        <v>-23</v>
+        <v>-117</v>
       </c>
       <c r="F11">
-        <v>-74</v>
+        <v>-31</v>
       </c>
       <c r="G11">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="H11">
-        <v>229</v>
+        <v>341</v>
       </c>
       <c r="I11">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="J11">
-        <v>227</v>
+        <v>337</v>
       </c>
       <c r="K11">
-        <v>128</v>
+        <v>258</v>
       </c>
       <c r="L11">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="M11">
-        <v>-25</v>
+        <v>-187</v>
       </c>
       <c r="N11">
-        <v>-125</v>
+        <v>-267</v>
       </c>
       <c r="O11">
-        <v>-72</v>
+        <v>-37</v>
       </c>
       <c r="P11">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="Q11">
-        <v>224</v>
+        <v>342</v>
       </c>
       <c r="R11">
-        <v>122</v>
+        <v>33</v>
       </c>
       <c r="S11">
-        <v>-121</v>
+        <v>-260</v>
       </c>
       <c r="T11">
-        <v>-77</v>
+        <v>-35</v>
       </c>
       <c r="U11">
-        <v>-171</v>
+        <v>-343</v>
       </c>
       <c r="V11">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="W11">
-        <v>226</v>
+        <v>342</v>
       </c>
       <c r="X11">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="Z11">
         <v>180</v>
       </c>
       <c r="AA11">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
         <v>90</v>
-      </c>
-      <c r="AC11">
-        <v>270</v>
       </c>
       <c r="AD11">
         <v>0</v>
       </c>
       <c r="AE11">
+        <v>90</v>
+      </c>
+      <c r="AF11">
+        <v>90</v>
+      </c>
+      <c r="AG11">
+        <v>270</v>
+      </c>
+      <c r="AH11">
         <v>180</v>
       </c>
-      <c r="AF11">
+      <c r="AI11">
         <v>270</v>
       </c>
-      <c r="AG11">
-        <v>90</v>
-      </c>
-      <c r="AH11">
+      <c r="AJ11">
         <v>270</v>
       </c>
-      <c r="AI11">
-        <v>0</v>
-      </c>
-      <c r="AJ11">
-        <v>90</v>
-      </c>
       <c r="AK11" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -3366,31 +3366,31 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AW11">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
@@ -3403,47 +3403,47 @@
         </is>
       </c>
       <c r="AZ11">
-        <v>175</v>
+        <v>-262.5</v>
       </c>
       <c r="BA11">
-        <v>225</v>
+        <v>112.5</v>
       </c>
       <c r="BB11">
-        <v>-225</v>
+        <v>337.5</v>
       </c>
       <c r="BC11">
-        <v>25</v>
+        <v>-37.5</v>
       </c>
       <c r="BD11">
-        <v>75</v>
+        <v>187.5</v>
       </c>
       <c r="BE11">
-        <v>-175</v>
+        <v>337.5</v>
       </c>
       <c r="BF11">
-        <v>-25</v>
+        <v>-112.5</v>
       </c>
       <c r="BG11">
-        <v>125</v>
+        <v>-262.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>yellow</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
+          <t>white</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
           <t>violet</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>green</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
@@ -3457,28 +3457,28 @@
         </is>
       </c>
       <c r="BN11">
-        <v>-75</v>
+        <v>37.5</v>
       </c>
       <c r="BO11">
-        <v>-175</v>
+        <v>-337.5</v>
       </c>
       <c r="BP11">
-        <v>-225</v>
+        <v>337.5</v>
       </c>
       <c r="BQ11">
-        <v>25</v>
+        <v>-37.5</v>
       </c>
       <c r="BR11">
-        <v>75</v>
+        <v>187.5</v>
       </c>
       <c r="BS11">
-        <v>-175</v>
+        <v>337.5</v>
       </c>
       <c r="BT11">
-        <v>-25</v>
+        <v>-112.5</v>
       </c>
       <c r="BU11">
-        <v>125</v>
+        <v>-262.5</v>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
@@ -3498,138 +3498,138 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>-29</v>
+        <v>-110</v>
       </c>
       <c r="B12">
-        <v>-228</v>
+        <v>-256</v>
       </c>
       <c r="C12">
-        <v>-126</v>
+        <v>-342</v>
       </c>
       <c r="D12">
-        <v>-78</v>
+        <v>-189</v>
       </c>
       <c r="E12">
-        <v>-25</v>
+        <v>-336</v>
       </c>
       <c r="F12">
-        <v>-221</v>
+        <v>-108</v>
       </c>
       <c r="G12">
-        <v>76</v>
+        <v>261</v>
       </c>
       <c r="H12">
-        <v>23</v>
+        <v>336</v>
       </c>
       <c r="I12">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="J12">
-        <v>227</v>
+        <v>31</v>
       </c>
       <c r="K12">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="L12">
-        <v>20</v>
+        <v>263</v>
       </c>
       <c r="M12">
-        <v>-124</v>
+        <v>-267</v>
       </c>
       <c r="N12">
-        <v>-25</v>
+        <v>-117</v>
       </c>
       <c r="O12">
-        <v>-73</v>
+        <v>-338</v>
       </c>
       <c r="P12">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="Q12">
-        <v>21</v>
+        <v>266</v>
       </c>
       <c r="R12">
-        <v>129</v>
+        <v>44</v>
       </c>
       <c r="S12">
-        <v>-223</v>
+        <v>-260</v>
       </c>
       <c r="T12">
-        <v>-20</v>
+        <v>-341</v>
       </c>
       <c r="U12">
-        <v>-121</v>
+        <v>-119</v>
       </c>
       <c r="V12">
-        <v>226</v>
+        <v>114</v>
       </c>
       <c r="W12">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="X12">
-        <v>73</v>
+        <v>345</v>
       </c>
       <c r="Y12">
+        <v>270</v>
+      </c>
+      <c r="Z12">
         <v>90</v>
-      </c>
-      <c r="Z12">
-        <v>270</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
+        <v>270</v>
+      </c>
+      <c r="AC12">
+        <v>90</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
         <v>180</v>
       </c>
-      <c r="AC12">
+      <c r="AG12">
         <v>180</v>
       </c>
-      <c r="AD12">
+      <c r="AH12">
+        <v>180</v>
+      </c>
+      <c r="AI12">
         <v>270</v>
       </c>
-      <c r="AE12">
+      <c r="AJ12">
         <v>90</v>
       </c>
-      <c r="AF12">
-        <v>270</v>
-      </c>
-      <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AH12">
-        <v>0</v>
-      </c>
-      <c r="AI12">
-        <v>90</v>
-      </c>
-      <c r="AJ12">
-        <v>180</v>
-      </c>
       <c r="AK12" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AP12" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="AW12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
@@ -3679,32 +3679,32 @@
         </is>
       </c>
       <c r="AZ12">
-        <v>125</v>
+        <v>-37.5</v>
       </c>
       <c r="BA12">
-        <v>125</v>
+        <v>112.5</v>
       </c>
       <c r="BB12">
-        <v>-225</v>
+        <v>-337.5</v>
       </c>
       <c r="BC12">
-        <v>225</v>
+        <v>-112.5</v>
       </c>
       <c r="BD12">
-        <v>25</v>
+        <v>112.5</v>
       </c>
       <c r="BE12">
-        <v>-225</v>
+        <v>337.5</v>
       </c>
       <c r="BF12">
-        <v>-75</v>
+        <v>-187.5</v>
       </c>
       <c r="BG12">
-        <v>-75</v>
+        <v>-262.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>red</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>violet</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
@@ -3724,37 +3724,37 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>d</t>
         </is>
       </c>
       <c r="BN12">
-        <v>125</v>
+        <v>112.5</v>
       </c>
       <c r="BO12">
-        <v>125</v>
+        <v>337.5</v>
       </c>
       <c r="BP12">
-        <v>-225</v>
+        <v>-337.5</v>
       </c>
       <c r="BQ12">
-        <v>225</v>
+        <v>-112.5</v>
       </c>
       <c r="BR12">
-        <v>25</v>
+        <v>112.5</v>
       </c>
       <c r="BS12">
-        <v>-225</v>
+        <v>337.5</v>
       </c>
       <c r="BT12">
-        <v>-75</v>
+        <v>-187.5</v>
       </c>
       <c r="BU12">
-        <v>-75</v>
+        <v>-262.5</v>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
@@ -3774,106 +3774,106 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>-226</v>
+        <v>-342</v>
       </c>
       <c r="B13">
-        <v>-171</v>
+        <v>-110</v>
       </c>
       <c r="C13">
-        <v>-27</v>
+        <v>-270</v>
       </c>
       <c r="D13">
-        <v>-127</v>
+        <v>-189</v>
       </c>
       <c r="E13">
-        <v>-22</v>
+        <v>-42</v>
       </c>
       <c r="F13">
-        <v>-230</v>
+        <v>-267</v>
       </c>
       <c r="G13">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="H13">
-        <v>222</v>
+        <v>119</v>
       </c>
       <c r="I13">
-        <v>22</v>
+        <v>258</v>
       </c>
       <c r="J13">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="K13">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="L13">
-        <v>227</v>
+        <v>37</v>
       </c>
       <c r="M13">
-        <v>-75</v>
+        <v>-337</v>
       </c>
       <c r="N13">
-        <v>-26</v>
+        <v>-39</v>
       </c>
       <c r="O13">
-        <v>-126</v>
+        <v>-269</v>
       </c>
       <c r="P13">
-        <v>24</v>
+        <v>193</v>
       </c>
       <c r="Q13">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="R13">
-        <v>180</v>
+        <v>337</v>
       </c>
       <c r="S13">
-        <v>-225</v>
+        <v>-109</v>
       </c>
       <c r="T13">
-        <v>-171</v>
+        <v>-263</v>
       </c>
       <c r="U13">
-        <v>-21</v>
+        <v>-333</v>
       </c>
       <c r="V13">
-        <v>222</v>
+        <v>33</v>
       </c>
       <c r="W13">
-        <v>177</v>
+        <v>262</v>
       </c>
       <c r="X13">
-        <v>29</v>
+        <v>184</v>
       </c>
       <c r="Y13">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="Z13">
         <v>90</v>
       </c>
       <c r="AA13">
+        <v>90</v>
+      </c>
+      <c r="AB13">
+        <v>270</v>
+      </c>
+      <c r="AC13">
         <v>0</v>
       </c>
-      <c r="AB13">
+      <c r="AD13">
         <v>180</v>
       </c>
-      <c r="AC13">
-        <v>90</v>
-      </c>
-      <c r="AD13">
+      <c r="AE13">
+        <v>180</v>
+      </c>
+      <c r="AF13">
+        <v>180</v>
+      </c>
+      <c r="AG13">
         <v>0</v>
       </c>
-      <c r="AE13">
+      <c r="AH13">
         <v>270</v>
-      </c>
-      <c r="AF13">
-        <v>270</v>
-      </c>
-      <c r="AG13">
-        <v>180</v>
-      </c>
-      <c r="AH13">
-        <v>90</v>
       </c>
       <c r="AI13">
         <v>0</v>
@@ -3913,36 +3913,36 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AW13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
@@ -3955,32 +3955,32 @@
         </is>
       </c>
       <c r="AZ13">
-        <v>-225</v>
+        <v>187.5</v>
       </c>
       <c r="BA13">
-        <v>125</v>
+        <v>-187.5</v>
       </c>
       <c r="BB13">
-        <v>175</v>
+        <v>-337.5</v>
       </c>
       <c r="BC13">
-        <v>-75</v>
+        <v>-337.5</v>
       </c>
       <c r="BD13">
-        <v>-125</v>
+        <v>-37.5</v>
       </c>
       <c r="BE13">
-        <v>-225</v>
+        <v>262.5</v>
       </c>
       <c r="BF13">
-        <v>-25</v>
+        <v>337.5</v>
       </c>
       <c r="BG13">
-        <v>25</v>
+        <v>-37.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>black</t>
+          <t>violet</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>violet</t>
+          <t>red</t>
         </is>
       </c>
       <c r="BK13" t="inlineStr">
@@ -4009,28 +4009,28 @@
         </is>
       </c>
       <c r="BN13">
-        <v>-25</v>
+        <v>337.5</v>
       </c>
       <c r="BO13">
-        <v>-175</v>
+        <v>337.5</v>
       </c>
       <c r="BP13">
-        <v>175</v>
+        <v>-337.5</v>
       </c>
       <c r="BQ13">
-        <v>-75</v>
+        <v>-337.5</v>
       </c>
       <c r="BR13">
-        <v>-125</v>
+        <v>-37.5</v>
       </c>
       <c r="BS13">
-        <v>-225</v>
+        <v>262.5</v>
       </c>
       <c r="BT13">
-        <v>-25</v>
+        <v>337.5</v>
       </c>
       <c r="BU13">
-        <v>25</v>
+        <v>-37.5</v>
       </c>
       <c r="BV13" t="inlineStr">
         <is>

--- a/test_phase_200.xlsx
+++ b/test_phase_200.xlsx
@@ -738,79 +738,79 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>-331</v>
+        <v>-201</v>
       </c>
       <c r="B2">
-        <v>-189</v>
+        <v>-377</v>
       </c>
       <c r="C2">
-        <v>-119</v>
+        <v>-285</v>
       </c>
       <c r="D2">
-        <v>-183</v>
+        <v>-36</v>
       </c>
       <c r="E2">
-        <v>-32</v>
+        <v>-117</v>
       </c>
       <c r="F2">
-        <v>-256</v>
+        <v>-213</v>
       </c>
       <c r="G2">
-        <v>339</v>
+        <v>43</v>
       </c>
       <c r="H2">
+        <v>215</v>
+      </c>
+      <c r="I2">
+        <v>371</v>
+      </c>
+      <c r="J2">
+        <v>203</v>
+      </c>
+      <c r="K2">
+        <v>36</v>
+      </c>
+      <c r="L2">
+        <v>131</v>
+      </c>
+      <c r="M2">
+        <v>-293</v>
+      </c>
+      <c r="N2">
+        <v>-39</v>
+      </c>
+      <c r="O2">
+        <v>-369</v>
+      </c>
+      <c r="P2">
         <v>34</v>
       </c>
-      <c r="I2">
-        <v>119</v>
-      </c>
-      <c r="J2">
-        <v>114</v>
-      </c>
-      <c r="K2">
-        <v>193</v>
-      </c>
-      <c r="L2">
-        <v>43</v>
-      </c>
-      <c r="M2">
-        <v>-115</v>
-      </c>
-      <c r="N2">
-        <v>-343</v>
-      </c>
-      <c r="O2">
-        <v>-183</v>
-      </c>
-      <c r="P2">
-        <v>342</v>
-      </c>
       <c r="Q2">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="R2">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="S2">
-        <v>-106</v>
+        <v>-292</v>
       </c>
       <c r="T2">
-        <v>-337</v>
+        <v>-204</v>
       </c>
       <c r="U2">
-        <v>-269</v>
+        <v>-130</v>
       </c>
       <c r="V2">
-        <v>189</v>
+        <v>133</v>
       </c>
       <c r="W2">
-        <v>108</v>
+        <v>298</v>
       </c>
       <c r="X2">
-        <v>265</v>
+        <v>34</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -819,31 +819,31 @@
         <v>180</v>
       </c>
       <c r="AB2">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AC2">
         <v>90</v>
       </c>
       <c r="AD2">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AE2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AF2">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AG2">
         <v>90</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AI2">
         <v>270</v>
       </c>
       <c r="AJ2">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -877,19 +877,19 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="AW2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -919,28 +919,28 @@
         </is>
       </c>
       <c r="AZ2">
-        <v>-187.5</v>
+        <v>290.5</v>
       </c>
       <c r="BA2">
-        <v>337.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BB2">
-        <v>-337.5</v>
+        <v>-124.5</v>
       </c>
       <c r="BC2">
-        <v>-112.5</v>
+        <v>124.5</v>
       </c>
       <c r="BD2">
-        <v>337.5</v>
+        <v>-290.5</v>
       </c>
       <c r="BE2">
-        <v>37.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BF2">
-        <v>112.5</v>
+        <v>41.5</v>
       </c>
       <c r="BG2">
-        <v>-337.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
@@ -949,12 +949,12 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>black</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>black</t>
+          <t>violet</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
@@ -964,37 +964,37 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>s</t>
         </is>
       </c>
       <c r="BN2">
-        <v>187.5</v>
+        <v>290.5</v>
       </c>
       <c r="BO2">
-        <v>-262.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BP2">
-        <v>-337.5</v>
+        <v>-124.5</v>
       </c>
       <c r="BQ2">
-        <v>-112.5</v>
+        <v>124.5</v>
       </c>
       <c r="BR2">
-        <v>337.5</v>
+        <v>-290.5</v>
       </c>
       <c r="BS2">
-        <v>37.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BT2">
-        <v>112.5</v>
+        <v>41.5</v>
       </c>
       <c r="BU2">
-        <v>-337.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
@@ -1014,112 +1014,112 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>-33</v>
+        <v>-202</v>
       </c>
       <c r="B3">
-        <v>-189</v>
+        <v>-294</v>
       </c>
       <c r="C3">
-        <v>-112</v>
+        <v>-376</v>
       </c>
       <c r="D3">
+        <v>-284</v>
+      </c>
+      <c r="E3">
+        <v>-43</v>
+      </c>
+      <c r="F3">
+        <v>-129</v>
+      </c>
+      <c r="G3">
+        <v>283</v>
+      </c>
+      <c r="H3">
+        <v>381</v>
+      </c>
+      <c r="I3">
+        <v>47</v>
+      </c>
+      <c r="J3">
+        <v>132</v>
+      </c>
+      <c r="K3">
+        <v>285</v>
+      </c>
+      <c r="L3">
+        <v>48</v>
+      </c>
+      <c r="M3">
         <v>-116</v>
       </c>
-      <c r="E3">
-        <v>-39</v>
-      </c>
-      <c r="F3">
-        <v>-194</v>
-      </c>
-      <c r="G3">
-        <v>109</v>
-      </c>
-      <c r="H3">
-        <v>263</v>
-      </c>
-      <c r="I3">
-        <v>39</v>
-      </c>
-      <c r="J3">
-        <v>342</v>
-      </c>
-      <c r="K3">
-        <v>40</v>
-      </c>
-      <c r="L3">
-        <v>269</v>
-      </c>
-      <c r="M3">
-        <v>-192</v>
-      </c>
       <c r="N3">
-        <v>-107</v>
+        <v>-41</v>
       </c>
       <c r="O3">
-        <v>-34</v>
+        <v>-367</v>
       </c>
       <c r="P3">
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="Q3">
-        <v>37</v>
+        <v>371</v>
       </c>
       <c r="R3">
-        <v>342</v>
+        <v>48</v>
       </c>
       <c r="S3">
-        <v>-109</v>
+        <v>-44</v>
       </c>
       <c r="T3">
-        <v>-30</v>
+        <v>-123</v>
       </c>
       <c r="U3">
-        <v>-338</v>
+        <v>-210</v>
       </c>
       <c r="V3">
-        <v>261</v>
+        <v>201</v>
       </c>
       <c r="W3">
-        <v>344</v>
+        <v>129</v>
       </c>
       <c r="X3">
-        <v>107</v>
+        <v>35</v>
       </c>
       <c r="Y3">
         <v>180</v>
       </c>
       <c r="Z3">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AA3">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AB3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AE3">
+        <v>270</v>
+      </c>
+      <c r="AF3">
         <v>180</v>
       </c>
-      <c r="AF3">
+      <c r="AG3">
         <v>90</v>
       </c>
-      <c r="AG3">
+      <c r="AH3">
         <v>180</v>
-      </c>
-      <c r="AH3">
-        <v>270</v>
       </c>
       <c r="AI3">
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
@@ -1133,39 +1133,39 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="AW3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1195,82 +1195,82 @@
         </is>
       </c>
       <c r="AZ3">
-        <v>-187.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BA3">
-        <v>187.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BB3">
-        <v>37.5</v>
+        <v>373.5</v>
       </c>
       <c r="BC3">
-        <v>337.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BD3">
-        <v>-337.5</v>
+        <v>207.5</v>
       </c>
       <c r="BE3">
-        <v>-112.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BF3">
-        <v>187.5</v>
+        <v>-290.5</v>
       </c>
       <c r="BG3">
-        <v>37.5</v>
+        <v>373.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>violet</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>violet</t>
+          <t>red</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
+          <t>black</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
           <t>yellow</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>d</t>
         </is>
       </c>
       <c r="BN3">
-        <v>-187.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BO3">
-        <v>187.5</v>
+        <v>290.5</v>
       </c>
       <c r="BP3">
-        <v>37.5</v>
+        <v>373.5</v>
       </c>
       <c r="BQ3">
-        <v>337.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BR3">
-        <v>-337.5</v>
+        <v>207.5</v>
       </c>
       <c r="BS3">
-        <v>-112.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BT3">
-        <v>187.5</v>
+        <v>-290.5</v>
       </c>
       <c r="BU3">
-        <v>37.5</v>
+        <v>373.5</v>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
@@ -1290,94 +1290,94 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>-338</v>
+        <v>-204</v>
       </c>
       <c r="B4">
-        <v>-270</v>
+        <v>-127</v>
       </c>
       <c r="C4">
-        <v>-107</v>
+        <v>-49</v>
       </c>
       <c r="D4">
-        <v>-259</v>
+        <v>-210</v>
       </c>
       <c r="E4">
-        <v>-36</v>
+        <v>-118</v>
       </c>
       <c r="F4">
-        <v>-110</v>
+        <v>-374</v>
       </c>
       <c r="G4">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="H4">
-        <v>257</v>
+        <v>36</v>
       </c>
       <c r="I4">
-        <v>182</v>
+        <v>297</v>
       </c>
       <c r="J4">
-        <v>331</v>
+        <v>36</v>
       </c>
       <c r="K4">
-        <v>35</v>
+        <v>381</v>
       </c>
       <c r="L4">
-        <v>109</v>
+        <v>283</v>
       </c>
       <c r="M4">
-        <v>-262</v>
+        <v>-297</v>
       </c>
       <c r="N4">
-        <v>-117</v>
+        <v>-47</v>
       </c>
       <c r="O4">
-        <v>-34</v>
+        <v>-366</v>
       </c>
       <c r="P4">
-        <v>265</v>
+        <v>41</v>
       </c>
       <c r="Q4">
-        <v>337</v>
+        <v>132</v>
       </c>
       <c r="R4">
-        <v>43</v>
+        <v>297</v>
       </c>
       <c r="S4">
-        <v>-116</v>
+        <v>-38</v>
       </c>
       <c r="T4">
-        <v>-40</v>
+        <v>-125</v>
       </c>
       <c r="U4">
-        <v>-268</v>
+        <v>-375</v>
       </c>
       <c r="V4">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="W4">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="X4">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="Y4">
+        <v>270</v>
+      </c>
+      <c r="Z4">
         <v>0</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
+        <v>90</v>
+      </c>
+      <c r="AB4">
+        <v>180</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
         <v>270</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>90</v>
-      </c>
-      <c r="AC4">
-        <v>180</v>
-      </c>
-      <c r="AD4">
-        <v>90</v>
       </c>
       <c r="AE4">
         <v>180</v>
@@ -1389,10 +1389,10 @@
         <v>180</v>
       </c>
       <c r="AH4">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ4">
         <v>90</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="AW4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1471,82 +1471,82 @@
         </is>
       </c>
       <c r="AZ4">
-        <v>-187.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BA4">
-        <v>-112.5</v>
+        <v>-124.5</v>
       </c>
       <c r="BB4">
-        <v>-337.5</v>
+        <v>-290.5</v>
       </c>
       <c r="BC4">
-        <v>-262.5</v>
+        <v>-290.5</v>
       </c>
       <c r="BD4">
-        <v>-37.5</v>
+        <v>124.5</v>
       </c>
       <c r="BE4">
-        <v>37.5</v>
+        <v>207.5</v>
       </c>
       <c r="BF4">
-        <v>187.5</v>
+        <v>290.5</v>
       </c>
       <c r="BG4">
-        <v>337.5</v>
+        <v>41.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>white</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
           <t>black</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>yellow</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>violet</t>
-        </is>
-      </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>d</t>
         </is>
       </c>
       <c r="BN4">
-        <v>-187.5</v>
+        <v>124.5</v>
       </c>
       <c r="BO4">
-        <v>-112.5</v>
+        <v>207.5</v>
       </c>
       <c r="BP4">
-        <v>-337.5</v>
+        <v>-290.5</v>
       </c>
       <c r="BQ4">
-        <v>-262.5</v>
+        <v>-290.5</v>
       </c>
       <c r="BR4">
-        <v>-37.5</v>
+        <v>124.5</v>
       </c>
       <c r="BS4">
-        <v>37.5</v>
+        <v>207.5</v>
       </c>
       <c r="BT4">
-        <v>187.5</v>
+        <v>290.5</v>
       </c>
       <c r="BU4">
-        <v>337.5</v>
+        <v>41.5</v>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
@@ -1566,116 +1566,116 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>-343</v>
+        <v>-379</v>
       </c>
       <c r="B5">
-        <v>-185</v>
+        <v>-289</v>
       </c>
       <c r="C5">
-        <v>-42</v>
+        <v>-206</v>
       </c>
       <c r="D5">
-        <v>-191</v>
+        <v>-376</v>
       </c>
       <c r="E5">
-        <v>-42</v>
+        <v>-289</v>
       </c>
       <c r="F5">
-        <v>-269</v>
+        <v>-117</v>
       </c>
       <c r="G5">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H5">
+        <v>122</v>
+      </c>
+      <c r="I5">
+        <v>205</v>
+      </c>
+      <c r="J5">
+        <v>210</v>
+      </c>
+      <c r="K5">
+        <v>298</v>
+      </c>
+      <c r="L5">
         <v>35</v>
       </c>
-      <c r="I5">
-        <v>259</v>
-      </c>
-      <c r="J5">
-        <v>340</v>
-      </c>
-      <c r="K5">
-        <v>120</v>
-      </c>
-      <c r="L5">
-        <v>267</v>
-      </c>
       <c r="M5">
-        <v>-186</v>
+        <v>-44</v>
       </c>
       <c r="N5">
-        <v>-259</v>
+        <v>-371</v>
       </c>
       <c r="O5">
-        <v>-116</v>
+        <v>-214</v>
       </c>
       <c r="P5">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="Q5">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="R5">
-        <v>331</v>
+        <v>368</v>
       </c>
       <c r="S5">
-        <v>-340</v>
+        <v>-209</v>
       </c>
       <c r="T5">
-        <v>-120</v>
+        <v>-50</v>
       </c>
       <c r="U5">
-        <v>-41</v>
+        <v>-117</v>
       </c>
       <c r="V5">
-        <v>262</v>
+        <v>209</v>
       </c>
       <c r="W5">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="X5">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="Y5">
         <v>90</v>
       </c>
       <c r="Z5">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AA5">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AB5">
         <v>90</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AD5">
+        <v>270</v>
+      </c>
+      <c r="AE5">
         <v>180</v>
-      </c>
-      <c r="AE5">
-        <v>270</v>
       </c>
       <c r="AF5">
         <v>0</v>
       </c>
       <c r="AG5">
+        <v>270</v>
+      </c>
+      <c r="AH5">
         <v>0</v>
       </c>
-      <c r="AH5">
+      <c r="AI5">
         <v>180</v>
       </c>
-      <c r="AI5">
-        <v>90</v>
-      </c>
       <c r="AJ5">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -1734,11 +1734,11 @@
         </is>
       </c>
       <c r="AW5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1747,82 +1747,82 @@
         </is>
       </c>
       <c r="AZ5">
-        <v>262.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BA5">
-        <v>262.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BB5">
-        <v>112.5</v>
+        <v>207.5</v>
       </c>
       <c r="BC5">
-        <v>-37.5</v>
+        <v>290.5</v>
       </c>
       <c r="BD5">
-        <v>-187.5</v>
+        <v>373.5</v>
       </c>
       <c r="BE5">
-        <v>-337.5</v>
+        <v>41.5</v>
       </c>
       <c r="BF5">
-        <v>-37.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BG5">
-        <v>112.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>violet</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>white</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>violet</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>white</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>d</t>
         </is>
       </c>
       <c r="BN5">
-        <v>262.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BO5">
-        <v>262.5</v>
+        <v>41.5</v>
       </c>
       <c r="BP5">
-        <v>112.5</v>
+        <v>207.5</v>
       </c>
       <c r="BQ5">
-        <v>-37.5</v>
+        <v>290.5</v>
       </c>
       <c r="BR5">
-        <v>-187.5</v>
+        <v>373.5</v>
       </c>
       <c r="BS5">
-        <v>-337.5</v>
+        <v>41.5</v>
       </c>
       <c r="BT5">
-        <v>-37.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BU5">
-        <v>112.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
@@ -1842,85 +1842,85 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>-332</v>
+        <v>-374</v>
       </c>
       <c r="B6">
-        <v>-111</v>
+        <v>-37</v>
       </c>
       <c r="C6">
-        <v>-181</v>
+        <v>-131</v>
       </c>
       <c r="D6">
-        <v>-263</v>
+        <v>-35</v>
       </c>
       <c r="E6">
-        <v>-115</v>
+        <v>-126</v>
       </c>
       <c r="F6">
-        <v>-40</v>
+        <v>-369</v>
       </c>
       <c r="G6">
-        <v>335</v>
+        <v>44</v>
       </c>
       <c r="H6">
-        <v>267</v>
+        <v>213</v>
       </c>
       <c r="I6">
-        <v>31</v>
+        <v>367</v>
       </c>
       <c r="J6">
-        <v>42</v>
+        <v>288</v>
       </c>
       <c r="K6">
+        <v>127</v>
+      </c>
+      <c r="L6">
+        <v>203</v>
+      </c>
+      <c r="M6">
+        <v>-120</v>
+      </c>
+      <c r="N6">
+        <v>-375</v>
+      </c>
+      <c r="O6">
+        <v>-41</v>
+      </c>
+      <c r="P6">
+        <v>209</v>
+      </c>
+      <c r="Q6">
+        <v>284</v>
+      </c>
+      <c r="R6">
+        <v>378</v>
+      </c>
+      <c r="S6">
+        <v>-132</v>
+      </c>
+      <c r="T6">
+        <v>-371</v>
+      </c>
+      <c r="U6">
+        <v>-214</v>
+      </c>
+      <c r="V6">
+        <v>377</v>
+      </c>
+      <c r="W6">
+        <v>122</v>
+      </c>
+      <c r="X6">
+        <v>41</v>
+      </c>
+      <c r="Y6">
         <v>180</v>
       </c>
-      <c r="L6">
-        <v>115</v>
-      </c>
-      <c r="M6">
-        <v>-341</v>
-      </c>
-      <c r="N6">
-        <v>-111</v>
-      </c>
-      <c r="O6">
-        <v>-36</v>
-      </c>
-      <c r="P6">
-        <v>269</v>
-      </c>
-      <c r="Q6">
-        <v>336</v>
-      </c>
-      <c r="R6">
-        <v>108</v>
-      </c>
-      <c r="S6">
-        <v>-343</v>
-      </c>
-      <c r="T6">
-        <v>-270</v>
-      </c>
-      <c r="U6">
-        <v>-111</v>
-      </c>
-      <c r="V6">
-        <v>37</v>
-      </c>
-      <c r="W6">
-        <v>333</v>
-      </c>
-      <c r="X6">
-        <v>267</v>
-      </c>
-      <c r="Y6">
+      <c r="Z6">
         <v>0</v>
       </c>
-      <c r="Z6">
-        <v>180</v>
-      </c>
       <c r="AA6">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AB6">
         <v>90</v>
@@ -1929,22 +1929,22 @@
         <v>270</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AE6">
         <v>270</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AG6">
         <v>180</v>
       </c>
       <c r="AH6">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AJ6">
         <v>90</v>
@@ -2023,49 +2023,49 @@
         </is>
       </c>
       <c r="AZ6">
-        <v>-337.5</v>
+        <v>124.5</v>
       </c>
       <c r="BA6">
-        <v>-37.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BB6">
-        <v>37.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BC6">
-        <v>-187.5</v>
+        <v>207.5</v>
       </c>
       <c r="BD6">
-        <v>262.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BE6">
-        <v>-337.5</v>
+        <v>373.5</v>
       </c>
       <c r="BF6">
-        <v>-187.5</v>
+        <v>290.5</v>
       </c>
       <c r="BG6">
-        <v>187.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>violet</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
           <t>yellow</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>violet</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>black</t>
-        </is>
-      </c>
       <c r="BL6" t="inlineStr">
         <is>
           <t>no</t>
@@ -2077,28 +2077,28 @@
         </is>
       </c>
       <c r="BN6">
-        <v>-337.5</v>
+        <v>124.5</v>
       </c>
       <c r="BO6">
-        <v>-37.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BP6">
-        <v>37.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BQ6">
-        <v>-187.5</v>
+        <v>207.5</v>
       </c>
       <c r="BR6">
-        <v>262.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BS6">
-        <v>-337.5</v>
+        <v>373.5</v>
       </c>
       <c r="BT6">
-        <v>-187.5</v>
+        <v>290.5</v>
       </c>
       <c r="BU6">
-        <v>187.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
@@ -2118,123 +2118,123 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>-114</v>
+        <v>-121</v>
       </c>
       <c r="B7">
-        <v>-343</v>
+        <v>-372</v>
       </c>
       <c r="C7">
-        <v>-186</v>
+        <v>-40</v>
       </c>
       <c r="D7">
-        <v>-35</v>
+        <v>-39</v>
       </c>
       <c r="E7">
-        <v>-119</v>
+        <v>-286</v>
       </c>
       <c r="F7">
-        <v>-189</v>
+        <v>-369</v>
       </c>
       <c r="G7">
-        <v>191</v>
+        <v>131</v>
       </c>
       <c r="H7">
-        <v>265</v>
+        <v>369</v>
       </c>
       <c r="I7">
-        <v>334</v>
+        <v>298</v>
       </c>
       <c r="J7">
-        <v>38</v>
+        <v>284</v>
       </c>
       <c r="K7">
-        <v>182</v>
+        <v>47</v>
       </c>
       <c r="L7">
-        <v>107</v>
+        <v>374</v>
       </c>
       <c r="M7">
-        <v>-341</v>
+        <v>-126</v>
       </c>
       <c r="N7">
-        <v>-182</v>
+        <v>-285</v>
       </c>
       <c r="O7">
-        <v>-258</v>
+        <v>-42</v>
       </c>
       <c r="P7">
-        <v>259</v>
+        <v>119</v>
       </c>
       <c r="Q7">
-        <v>341</v>
+        <v>372</v>
       </c>
       <c r="R7">
-        <v>33</v>
+        <v>291</v>
       </c>
       <c r="S7">
-        <v>-344</v>
+        <v>-380</v>
       </c>
       <c r="T7">
-        <v>-113</v>
+        <v>-292</v>
       </c>
       <c r="U7">
-        <v>-32</v>
+        <v>-201</v>
       </c>
       <c r="V7">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="W7">
-        <v>340</v>
+        <v>373</v>
       </c>
       <c r="X7">
-        <v>120</v>
+        <v>295</v>
       </c>
       <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
         <v>90</v>
       </c>
-      <c r="Z7">
+      <c r="AA7">
+        <v>90</v>
+      </c>
+      <c r="AB7">
         <v>0</v>
       </c>
-      <c r="AA7">
-        <v>180</v>
-      </c>
-      <c r="AB7">
+      <c r="AC7">
+        <v>90</v>
+      </c>
+      <c r="AD7">
         <v>270</v>
-      </c>
-      <c r="AC7">
-        <v>270</v>
-      </c>
-      <c r="AD7">
-        <v>90</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
+        <v>180</v>
+      </c>
+      <c r="AG7">
         <v>270</v>
       </c>
-      <c r="AG7">
+      <c r="AH7">
         <v>180</v>
       </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
       <c r="AI7">
+        <v>270</v>
+      </c>
+      <c r="AJ7">
         <v>180</v>
       </c>
-      <c r="AJ7">
-        <v>90</v>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AM7" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="AW7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -2299,49 +2299,49 @@
         </is>
       </c>
       <c r="AZ7">
-        <v>-262.5</v>
+        <v>-124.5</v>
       </c>
       <c r="BA7">
-        <v>112.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BB7">
-        <v>-112.5</v>
+        <v>41.5</v>
       </c>
       <c r="BC7">
-        <v>337.5</v>
+        <v>373.5</v>
       </c>
       <c r="BD7">
-        <v>37.5</v>
+        <v>373.5</v>
       </c>
       <c r="BE7">
-        <v>-337.5</v>
+        <v>207.5</v>
       </c>
       <c r="BF7">
-        <v>187.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BG7">
-        <v>-187.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>violet</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>black</t>
-        </is>
-      </c>
       <c r="BL7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2353,28 +2353,28 @@
         </is>
       </c>
       <c r="BN7">
-        <v>262.5</v>
+        <v>207.5</v>
       </c>
       <c r="BO7">
-        <v>-37.5</v>
+        <v>124.5</v>
       </c>
       <c r="BP7">
-        <v>-112.5</v>
+        <v>41.5</v>
       </c>
       <c r="BQ7">
-        <v>337.5</v>
+        <v>373.5</v>
       </c>
       <c r="BR7">
-        <v>37.5</v>
+        <v>373.5</v>
       </c>
       <c r="BS7">
-        <v>-337.5</v>
+        <v>207.5</v>
       </c>
       <c r="BT7">
-        <v>187.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BU7">
-        <v>-187.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
@@ -2394,109 +2394,109 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>-185</v>
+        <v>-368</v>
       </c>
       <c r="B8">
-        <v>-333</v>
+        <v>-123</v>
       </c>
       <c r="C8">
-        <v>-269</v>
+        <v>-42</v>
       </c>
       <c r="D8">
-        <v>-183</v>
+        <v>-126</v>
       </c>
       <c r="E8">
-        <v>-340</v>
+        <v>-376</v>
       </c>
       <c r="F8">
-        <v>-34</v>
+        <v>-207</v>
       </c>
       <c r="G8">
-        <v>110</v>
+        <v>282</v>
       </c>
       <c r="H8">
-        <v>337</v>
+        <v>36</v>
       </c>
       <c r="I8">
-        <v>257</v>
+        <v>377</v>
       </c>
       <c r="J8">
-        <v>109</v>
+        <v>366</v>
       </c>
       <c r="K8">
-        <v>270</v>
+        <v>45</v>
       </c>
       <c r="L8">
-        <v>337</v>
+        <v>124</v>
       </c>
       <c r="M8">
-        <v>-39</v>
+        <v>-210</v>
       </c>
       <c r="N8">
-        <v>-267</v>
+        <v>-117</v>
       </c>
       <c r="O8">
-        <v>-106</v>
+        <v>-377</v>
       </c>
       <c r="P8">
-        <v>338</v>
+        <v>205</v>
       </c>
       <c r="Q8">
-        <v>186</v>
+        <v>282</v>
       </c>
       <c r="R8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="S8">
-        <v>-333</v>
+        <v>-120</v>
       </c>
       <c r="T8">
-        <v>-181</v>
+        <v>-290</v>
       </c>
       <c r="U8">
-        <v>-44</v>
+        <v>-200</v>
       </c>
       <c r="V8">
-        <v>258</v>
+        <v>34</v>
       </c>
       <c r="W8">
-        <v>115</v>
+        <v>378</v>
       </c>
       <c r="X8">
-        <v>40</v>
+        <v>128</v>
       </c>
       <c r="Y8">
         <v>0</v>
       </c>
       <c r="Z8">
+        <v>270</v>
+      </c>
+      <c r="AA8">
+        <v>180</v>
+      </c>
+      <c r="AB8">
         <v>0</v>
       </c>
-      <c r="AA8">
+      <c r="AC8">
+        <v>180</v>
+      </c>
+      <c r="AD8">
+        <v>90</v>
+      </c>
+      <c r="AE8">
+        <v>90</v>
+      </c>
+      <c r="AF8">
         <v>0</v>
       </c>
-      <c r="AB8">
+      <c r="AG8">
+        <v>270</v>
+      </c>
+      <c r="AH8">
         <v>90</v>
       </c>
-      <c r="AC8">
-        <v>90</v>
-      </c>
-      <c r="AD8">
+      <c r="AI8">
         <v>270</v>
-      </c>
-      <c r="AE8">
-        <v>180</v>
-      </c>
-      <c r="AF8">
-        <v>270</v>
-      </c>
-      <c r="AG8">
-        <v>180</v>
-      </c>
-      <c r="AH8">
-        <v>270</v>
-      </c>
-      <c r="AI8">
-        <v>90</v>
       </c>
       <c r="AJ8">
         <v>180</v>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -2562,7 +2562,7 @@
         </is>
       </c>
       <c r="AW8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -2575,82 +2575,82 @@
         </is>
       </c>
       <c r="AZ8">
-        <v>112.5</v>
+        <v>207.5</v>
       </c>
       <c r="BA8">
-        <v>112.5</v>
+        <v>-124.5</v>
       </c>
       <c r="BB8">
-        <v>262.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BC8">
-        <v>-337.5</v>
+        <v>207.5</v>
       </c>
       <c r="BD8">
-        <v>-37.5</v>
+        <v>373.5</v>
       </c>
       <c r="BE8">
-        <v>-37.5</v>
+        <v>-290.5</v>
       </c>
       <c r="BF8">
-        <v>-337.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BG8">
-        <v>-187.5</v>
+        <v>373.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>violet</t>
+          <t>red</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>green</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>black</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>s</t>
         </is>
       </c>
       <c r="BN8">
-        <v>-187.5</v>
+        <v>207.5</v>
       </c>
       <c r="BO8">
-        <v>-37.5</v>
+        <v>-124.5</v>
       </c>
       <c r="BP8">
-        <v>262.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BQ8">
-        <v>-337.5</v>
+        <v>207.5</v>
       </c>
       <c r="BR8">
-        <v>-37.5</v>
+        <v>373.5</v>
       </c>
       <c r="BS8">
-        <v>-37.5</v>
+        <v>-290.5</v>
       </c>
       <c r="BT8">
-        <v>-337.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BU8">
-        <v>-187.5</v>
+        <v>373.5</v>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
@@ -2670,85 +2670,85 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>-186</v>
+        <v>-380</v>
       </c>
       <c r="B9">
-        <v>-256</v>
+        <v>-122</v>
       </c>
       <c r="C9">
-        <v>-105</v>
+        <v>-208</v>
       </c>
       <c r="D9">
-        <v>-30</v>
+        <v>-35</v>
       </c>
       <c r="E9">
-        <v>-332</v>
+        <v>-374</v>
       </c>
       <c r="F9">
-        <v>-256</v>
+        <v>-290</v>
       </c>
       <c r="G9">
-        <v>31</v>
+        <v>378</v>
       </c>
       <c r="H9">
-        <v>340</v>
+        <v>130</v>
       </c>
       <c r="I9">
-        <v>108</v>
+        <v>294</v>
       </c>
       <c r="J9">
-        <v>341</v>
+        <v>46</v>
       </c>
       <c r="K9">
-        <v>115</v>
+        <v>212</v>
       </c>
       <c r="L9">
-        <v>257</v>
+        <v>367</v>
       </c>
       <c r="M9">
-        <v>-339</v>
+        <v>-40</v>
       </c>
       <c r="N9">
-        <v>-181</v>
+        <v>-213</v>
       </c>
       <c r="O9">
-        <v>-109</v>
+        <v>-289</v>
       </c>
       <c r="P9">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="Q9">
-        <v>34</v>
+        <v>205</v>
       </c>
       <c r="R9">
-        <v>339</v>
+        <v>287</v>
       </c>
       <c r="S9">
-        <v>-109</v>
+        <v>-290</v>
       </c>
       <c r="T9">
-        <v>-194</v>
+        <v>-38</v>
       </c>
       <c r="U9">
-        <v>-32</v>
+        <v>-369</v>
       </c>
       <c r="V9">
-        <v>341</v>
+        <v>283</v>
       </c>
       <c r="W9">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="X9">
-        <v>269</v>
+        <v>373</v>
       </c>
       <c r="Y9">
         <v>0</v>
       </c>
       <c r="Z9">
+        <v>180</v>
+      </c>
+      <c r="AA9">
         <v>270</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
       </c>
       <c r="AB9">
         <v>270</v>
@@ -2757,22 +2757,22 @@
         <v>180</v>
       </c>
       <c r="AD9">
+        <v>90</v>
+      </c>
+      <c r="AE9">
+        <v>90</v>
+      </c>
+      <c r="AF9">
         <v>0</v>
       </c>
-      <c r="AE9">
+      <c r="AG9">
         <v>270</v>
       </c>
-      <c r="AF9">
+      <c r="AH9">
         <v>180</v>
       </c>
-      <c r="AG9">
-        <v>180</v>
-      </c>
-      <c r="AH9">
-        <v>90</v>
-      </c>
       <c r="AI9">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
         <v>90</v>
@@ -2784,44 +2784,44 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="AW9">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2851,28 +2851,28 @@
         </is>
       </c>
       <c r="AZ9">
-        <v>-112.5</v>
+        <v>290.5</v>
       </c>
       <c r="BA9">
-        <v>-187.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BB9">
-        <v>-337.5</v>
+        <v>124.5</v>
       </c>
       <c r="BC9">
-        <v>-337.5</v>
+        <v>41.5</v>
       </c>
       <c r="BD9">
-        <v>262.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BE9">
-        <v>112.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BF9">
-        <v>112.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BG9">
-        <v>-37.5</v>
+        <v>290.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
@@ -2881,19 +2881,19 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>violet</t>
+          <t>black</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
           <t>yellow</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
       <c r="BL9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2905,28 +2905,28 @@
         </is>
       </c>
       <c r="BN9">
-        <v>262.5</v>
+        <v>-290.5</v>
       </c>
       <c r="BO9">
-        <v>37.5</v>
+        <v>373.5</v>
       </c>
       <c r="BP9">
-        <v>-337.5</v>
+        <v>124.5</v>
       </c>
       <c r="BQ9">
-        <v>-337.5</v>
+        <v>41.5</v>
       </c>
       <c r="BR9">
-        <v>262.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BS9">
-        <v>112.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BT9">
-        <v>112.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BU9">
-        <v>-37.5</v>
+        <v>290.5</v>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
@@ -2946,112 +2946,112 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>-105</v>
+        <v>-374</v>
       </c>
       <c r="B10">
-        <v>-44</v>
+        <v>-208</v>
       </c>
       <c r="C10">
-        <v>-188</v>
+        <v>-295</v>
       </c>
       <c r="D10">
-        <v>-185</v>
+        <v>-284</v>
       </c>
       <c r="E10">
         <v>-33</v>
       </c>
       <c r="F10">
-        <v>-337</v>
+        <v>-132</v>
       </c>
       <c r="G10">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="H10">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="I10">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="J10">
-        <v>194</v>
+        <v>49</v>
       </c>
       <c r="K10">
-        <v>256</v>
+        <v>204</v>
       </c>
       <c r="L10">
-        <v>338</v>
+        <v>133</v>
       </c>
       <c r="M10">
-        <v>-30</v>
+        <v>-124</v>
       </c>
       <c r="N10">
-        <v>-114</v>
+        <v>-42</v>
       </c>
       <c r="O10">
-        <v>-269</v>
+        <v>-380</v>
       </c>
       <c r="P10">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="Q10">
-        <v>105</v>
+        <v>285</v>
       </c>
       <c r="R10">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="S10">
-        <v>-180</v>
+        <v>-206</v>
       </c>
       <c r="T10">
-        <v>-32</v>
+        <v>-128</v>
       </c>
       <c r="U10">
-        <v>-111</v>
+        <v>-366</v>
       </c>
       <c r="V10">
-        <v>109</v>
+        <v>202</v>
       </c>
       <c r="W10">
-        <v>258</v>
+        <v>36</v>
       </c>
       <c r="X10">
-        <v>181</v>
+        <v>378</v>
       </c>
       <c r="Y10">
         <v>90</v>
       </c>
       <c r="Z10">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AA10">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AB10">
         <v>0</v>
       </c>
       <c r="AC10">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AD10">
         <v>0</v>
       </c>
       <c r="AE10">
+        <v>270</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>90</v>
+      </c>
+      <c r="AH10">
         <v>180</v>
-      </c>
-      <c r="AF10">
-        <v>270</v>
-      </c>
-      <c r="AG10">
-        <v>180</v>
-      </c>
-      <c r="AH10">
-        <v>270</v>
       </c>
       <c r="AI10">
         <v>270</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="AW10">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -3127,82 +3127,82 @@
         </is>
       </c>
       <c r="AZ10">
-        <v>337.5</v>
+        <v>-290.5</v>
       </c>
       <c r="BA10">
-        <v>-262.5</v>
+        <v>-290.5</v>
       </c>
       <c r="BB10">
-        <v>-187.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BC10">
-        <v>337.5</v>
+        <v>-124.5</v>
       </c>
       <c r="BD10">
-        <v>187.5</v>
+        <v>373.5</v>
       </c>
       <c r="BE10">
-        <v>-112.5</v>
+        <v>124.5</v>
       </c>
       <c r="BF10">
-        <v>37.5</v>
+        <v>207.5</v>
       </c>
       <c r="BG10">
-        <v>187.5</v>
+        <v>373.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>white</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
           <t>red</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>black</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>yellow</t>
-        </is>
-      </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>s</t>
         </is>
       </c>
       <c r="BN10">
-        <v>112.5</v>
+        <v>-290.5</v>
       </c>
       <c r="BO10">
-        <v>37.5</v>
+        <v>-290.5</v>
       </c>
       <c r="BP10">
-        <v>-187.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BQ10">
-        <v>337.5</v>
+        <v>-124.5</v>
       </c>
       <c r="BR10">
-        <v>187.5</v>
+        <v>373.5</v>
       </c>
       <c r="BS10">
-        <v>-112.5</v>
+        <v>124.5</v>
       </c>
       <c r="BT10">
-        <v>37.5</v>
+        <v>207.5</v>
       </c>
       <c r="BU10">
-        <v>187.5</v>
+        <v>373.5</v>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
@@ -3222,116 +3222,116 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>-115</v>
+        <v>-50</v>
       </c>
       <c r="B11">
-        <v>-343</v>
+        <v>-120</v>
       </c>
       <c r="C11">
-        <v>-262</v>
+        <v>-376</v>
       </c>
       <c r="D11">
-        <v>-257</v>
+        <v>-209</v>
       </c>
       <c r="E11">
-        <v>-117</v>
+        <v>-126</v>
       </c>
       <c r="F11">
-        <v>-31</v>
+        <v>-370</v>
       </c>
       <c r="G11">
-        <v>186</v>
+        <v>371</v>
       </c>
       <c r="H11">
-        <v>341</v>
+        <v>292</v>
       </c>
       <c r="I11">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J11">
-        <v>337</v>
+        <v>215</v>
       </c>
       <c r="K11">
-        <v>258</v>
+        <v>46</v>
       </c>
       <c r="L11">
-        <v>184</v>
+        <v>121</v>
       </c>
       <c r="M11">
-        <v>-187</v>
+        <v>-283</v>
       </c>
       <c r="N11">
-        <v>-267</v>
+        <v>-50</v>
       </c>
       <c r="O11">
-        <v>-37</v>
+        <v>-215</v>
       </c>
       <c r="P11">
-        <v>112</v>
+        <v>213</v>
       </c>
       <c r="Q11">
-        <v>342</v>
+        <v>127</v>
       </c>
       <c r="R11">
-        <v>33</v>
+        <v>374</v>
       </c>
       <c r="S11">
-        <v>-260</v>
+        <v>-366</v>
       </c>
       <c r="T11">
-        <v>-35</v>
+        <v>-210</v>
       </c>
       <c r="U11">
-        <v>-343</v>
+        <v>-296</v>
       </c>
       <c r="V11">
-        <v>194</v>
+        <v>123</v>
       </c>
       <c r="W11">
-        <v>342</v>
+        <v>283</v>
       </c>
       <c r="X11">
-        <v>117</v>
+        <v>213</v>
       </c>
       <c r="Y11">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="Z11">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AC11">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AE11">
         <v>90</v>
       </c>
       <c r="AF11">
+        <v>270</v>
+      </c>
+      <c r="AG11">
         <v>90</v>
-      </c>
-      <c r="AG11">
-        <v>270</v>
       </c>
       <c r="AH11">
         <v>180</v>
       </c>
       <c r="AI11">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AJ11">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -3386,15 +3386,15 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AW11">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -3403,28 +3403,28 @@
         </is>
       </c>
       <c r="AZ11">
-        <v>-262.5</v>
+        <v>-290.5</v>
       </c>
       <c r="BA11">
-        <v>112.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BB11">
-        <v>337.5</v>
+        <v>-124.5</v>
       </c>
       <c r="BC11">
-        <v>-37.5</v>
+        <v>41.5</v>
       </c>
       <c r="BD11">
-        <v>187.5</v>
+        <v>290.5</v>
       </c>
       <c r="BE11">
-        <v>337.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BF11">
-        <v>-112.5</v>
+        <v>41.5</v>
       </c>
       <c r="BG11">
-        <v>-262.5</v>
+        <v>290.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
@@ -3438,47 +3438,47 @@
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>violet</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>black</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>s</t>
         </is>
       </c>
       <c r="BN11">
-        <v>37.5</v>
+        <v>-290.5</v>
       </c>
       <c r="BO11">
-        <v>-337.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BP11">
-        <v>337.5</v>
+        <v>-124.5</v>
       </c>
       <c r="BQ11">
-        <v>-37.5</v>
+        <v>41.5</v>
       </c>
       <c r="BR11">
-        <v>187.5</v>
+        <v>290.5</v>
       </c>
       <c r="BS11">
-        <v>337.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BT11">
-        <v>-112.5</v>
+        <v>41.5</v>
       </c>
       <c r="BU11">
-        <v>-262.5</v>
+        <v>290.5</v>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
@@ -3498,113 +3498,113 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>-110</v>
+        <v>-377</v>
       </c>
       <c r="B12">
-        <v>-256</v>
+        <v>-290</v>
       </c>
       <c r="C12">
-        <v>-342</v>
+        <v>-39</v>
       </c>
       <c r="D12">
-        <v>-189</v>
+        <v>-213</v>
       </c>
       <c r="E12">
-        <v>-336</v>
+        <v>-372</v>
       </c>
       <c r="F12">
-        <v>-108</v>
+        <v>-44</v>
       </c>
       <c r="G12">
-        <v>261</v>
+        <v>210</v>
       </c>
       <c r="H12">
-        <v>336</v>
+        <v>33</v>
       </c>
       <c r="I12">
-        <v>116</v>
+        <v>293</v>
       </c>
       <c r="J12">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="K12">
-        <v>116</v>
+        <v>213</v>
       </c>
       <c r="L12">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="M12">
-        <v>-267</v>
+        <v>-213</v>
       </c>
       <c r="N12">
-        <v>-117</v>
+        <v>-287</v>
       </c>
       <c r="O12">
-        <v>-338</v>
+        <v>-118</v>
       </c>
       <c r="P12">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="Q12">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="R12">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="S12">
-        <v>-260</v>
+        <v>-36</v>
       </c>
       <c r="T12">
-        <v>-341</v>
+        <v>-382</v>
       </c>
       <c r="U12">
-        <v>-119</v>
+        <v>-201</v>
       </c>
       <c r="V12">
-        <v>114</v>
+        <v>291</v>
       </c>
       <c r="W12">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="X12">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="Y12">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>180</v>
+      </c>
+      <c r="AB12">
+        <v>180</v>
+      </c>
+      <c r="AC12">
+        <v>180</v>
+      </c>
+      <c r="AD12">
         <v>90</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>270</v>
-      </c>
-      <c r="AC12">
-        <v>90</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AG12">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AH12">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
         <v>270</v>
       </c>
-      <c r="AJ12">
-        <v>90</v>
-      </c>
       <c r="AK12" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -3627,29 +3627,29 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AT12" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -3666,11 +3666,11 @@
         </is>
       </c>
       <c r="AW12">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -3679,49 +3679,49 @@
         </is>
       </c>
       <c r="AZ12">
-        <v>-37.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BA12">
-        <v>112.5</v>
+        <v>290.5</v>
       </c>
       <c r="BB12">
-        <v>-337.5</v>
+        <v>373.5</v>
       </c>
       <c r="BC12">
-        <v>-112.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BD12">
-        <v>112.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BE12">
-        <v>337.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BF12">
-        <v>-187.5</v>
+        <v>124.5</v>
       </c>
       <c r="BG12">
-        <v>-262.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>black</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>red</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>yellow</t>
-        </is>
-      </c>
       <c r="BJ12" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
           <t>violet</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
       <c r="BL12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3733,28 +3733,28 @@
         </is>
       </c>
       <c r="BN12">
-        <v>112.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BO12">
-        <v>337.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BP12">
-        <v>-337.5</v>
+        <v>373.5</v>
       </c>
       <c r="BQ12">
-        <v>-112.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BR12">
-        <v>112.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BS12">
-        <v>337.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BT12">
-        <v>-187.5</v>
+        <v>124.5</v>
       </c>
       <c r="BU12">
-        <v>-262.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
@@ -3774,116 +3774,116 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>-342</v>
+        <v>-216</v>
       </c>
       <c r="B13">
-        <v>-110</v>
+        <v>-293</v>
       </c>
       <c r="C13">
-        <v>-270</v>
+        <v>-35</v>
       </c>
       <c r="D13">
-        <v>-189</v>
+        <v>-118</v>
       </c>
       <c r="E13">
-        <v>-42</v>
+        <v>-376</v>
       </c>
       <c r="F13">
-        <v>-267</v>
+        <v>-299</v>
       </c>
       <c r="G13">
-        <v>182</v>
+        <v>49</v>
       </c>
       <c r="H13">
-        <v>119</v>
+        <v>201</v>
       </c>
       <c r="I13">
-        <v>258</v>
+        <v>125</v>
       </c>
       <c r="J13">
-        <v>255</v>
+        <v>213</v>
       </c>
       <c r="K13">
-        <v>110</v>
+        <v>297</v>
       </c>
       <c r="L13">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="M13">
-        <v>-337</v>
+        <v>-286</v>
       </c>
       <c r="N13">
-        <v>-39</v>
+        <v>-132</v>
       </c>
       <c r="O13">
-        <v>-269</v>
+        <v>-378</v>
       </c>
       <c r="P13">
-        <v>193</v>
+        <v>379</v>
       </c>
       <c r="Q13">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="R13">
-        <v>337</v>
+        <v>39</v>
       </c>
       <c r="S13">
-        <v>-109</v>
+        <v>-375</v>
       </c>
       <c r="T13">
-        <v>-263</v>
+        <v>-294</v>
       </c>
       <c r="U13">
-        <v>-333</v>
+        <v>-213</v>
       </c>
       <c r="V13">
-        <v>33</v>
+        <v>294</v>
       </c>
       <c r="W13">
-        <v>262</v>
+        <v>213</v>
       </c>
       <c r="X13">
-        <v>184</v>
+        <v>44</v>
       </c>
       <c r="Y13">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="Z13">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AA13">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AB13">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AC13">
         <v>0</v>
       </c>
       <c r="AD13">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AE13">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AF13">
         <v>180</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AH13">
         <v>270</v>
       </c>
       <c r="AI13">
+        <v>270</v>
+      </c>
+      <c r="AJ13">
         <v>0</v>
       </c>
-      <c r="AJ13">
-        <v>270</v>
-      </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -3938,11 +3938,11 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AW13">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
@@ -3955,42 +3955,42 @@
         </is>
       </c>
       <c r="AZ13">
-        <v>187.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BA13">
-        <v>-187.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BB13">
-        <v>-337.5</v>
+        <v>290.5</v>
       </c>
       <c r="BC13">
-        <v>-337.5</v>
+        <v>41.5</v>
       </c>
       <c r="BD13">
-        <v>-37.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BE13">
-        <v>262.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BF13">
-        <v>337.5</v>
+        <v>124.5</v>
       </c>
       <c r="BG13">
-        <v>-37.5</v>
+        <v>207.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>violet</t>
+          <t>white</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>green</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>black</t>
         </is>
       </c>
       <c r="BK13" t="inlineStr">
@@ -4000,37 +4000,37 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>s</t>
         </is>
       </c>
       <c r="BN13">
-        <v>337.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BO13">
-        <v>337.5</v>
+        <v>-207.5</v>
       </c>
       <c r="BP13">
-        <v>-337.5</v>
+        <v>290.5</v>
       </c>
       <c r="BQ13">
-        <v>-337.5</v>
+        <v>41.5</v>
       </c>
       <c r="BR13">
-        <v>-37.5</v>
+        <v>-41.5</v>
       </c>
       <c r="BS13">
-        <v>262.5</v>
+        <v>-373.5</v>
       </c>
       <c r="BT13">
-        <v>337.5</v>
+        <v>124.5</v>
       </c>
       <c r="BU13">
-        <v>-37.5</v>
+        <v>207.5</v>
       </c>
       <c r="BV13" t="inlineStr">
         <is>
